--- a/03_Outputs/Agroindustrial_Occidente/05_Economia/economia.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/05_Economia/economia.xlsx
@@ -8574,10 +8574,8 @@
       <c r="F11" s="118">
         <v>61.9332830446575</v>
       </c>
-      <c r="G11" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G11" s="120">
+        <v>0.0510421819085717</v>
       </c>
       <c r="H11" s="122">
         <v>4.08100761620658</v>
@@ -8815,7 +8813,7 @@
         <v>134.152206273554</v>
       </c>
       <c r="G15" s="121">
-        <v>22.6799701634777</v>
+        <v>22.7310123453863</v>
       </c>
       <c r="H15" s="123">
         <v>11.4040011746576</v>
@@ -8873,10 +8871,8 @@
       <c r="F16" s="118">
         <v>4.15549956764331</v>
       </c>
-      <c r="G16" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G16" s="120">
+        <v>0.0758132944825119</v>
       </c>
       <c r="H16" s="122">
         <v>0.587847402604111</v>
@@ -9232,7 +9228,7 @@
         <v>157.27030012418</v>
       </c>
       <c r="G22" s="121">
-        <v>0.108150673925239</v>
+        <v>0.183963968407751</v>
       </c>
       <c r="H22" s="123">
         <v>11.9636917427868</v>
@@ -10000,10 +9996,8 @@
       <c r="F35" s="118">
         <v>27.5045273134215</v>
       </c>
-      <c r="G35" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G35" s="120">
+        <v>0.0641111587234056</v>
       </c>
       <c r="H35" s="122">
         <v>0.507641577466941</v>
@@ -10064,7 +10058,7 @@
         <v>158.377808080261</v>
       </c>
       <c r="G36" s="121">
-        <v>18.8479901298843</v>
+        <v>18.9121012886077</v>
       </c>
       <c r="H36" s="123">
         <v>7.3458195955848</v>
@@ -10181,10 +10175,8 @@
       <c r="F38" s="118">
         <v>24.9729880924309</v>
       </c>
-      <c r="G38" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G38" s="120">
+        <v>0.0325828181687936</v>
       </c>
       <c r="H38" s="122">
         <v>3.51605181667596</v>
@@ -10481,7 +10473,7 @@
         <v>172.393635200834</v>
       </c>
       <c r="G43" s="121">
-        <v>25.6938594569227</v>
+        <v>25.7264422750914</v>
       </c>
       <c r="H43" s="123">
         <v>9.82728419128044</v>
@@ -11369,10 +11361,8 @@
       <c r="F58" s="118">
         <v>9.42487770258907</v>
       </c>
-      <c r="G58" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G58" s="120">
+        <v>0.018839023433154</v>
       </c>
       <c r="H58" s="122">
         <v>0.250626122172702</v>
@@ -11548,10 +11538,8 @@
       <c r="F61" s="118">
         <v>31.3873812278827</v>
       </c>
-      <c r="G61" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G61" s="120">
+        <v>0.0201272286175206</v>
       </c>
       <c r="H61" s="122">
         <v>2.49551868564872</v>
@@ -11730,7 +11718,7 @@
         <v>146.119857830552</v>
       </c>
       <c r="G64" s="121">
-        <v>52.6789284682155</v>
+        <v>52.7178947202661</v>
       </c>
       <c r="H64" s="123">
         <v>16.2776891588785</v>
